--- a/sheets/조재수대금교본/검수/봄날은 간다.xlsx
+++ b/sheets/조재수대금교본/검수/봄날은 간다.xlsx
@@ -2602,7 +2602,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應∽</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2643,7 +2643,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -2654,16 +2654,11 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -2714,17 +2709,12 @@
         </is>
       </c>
       <c r="I6" s="22"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2783,7 +2773,7 @@
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-∽林仲</t>
+林仲</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -2808,21 +2798,15 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒣∽
-‹</t>
+          <t xml:space="preserve">㒣</t>
         </is>
       </c>
       <c r="E9" s="22"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -2862,7 +2846,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應
-潢⊏
+潢
 㴌</t>
         </is>
       </c>
@@ -2950,23 +2934,13 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-ﾉ
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H13" s="21"/>
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
@@ -2995,8 +2969,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-ﾉ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/봄날은 간다.xlsx
+++ b/sheets/조재수대금교본/검수/봄날은 간다.xlsx
@@ -2602,7 +2602,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應</t>
+          <t xml:space="preserve">應∽</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2643,7 +2643,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -2773,7 +2773,7 @@
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-林仲</t>
+∽林仲</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -2798,7 +2798,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒣</t>
+          <t xml:space="preserve">㒣∽</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -2846,7 +2846,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應
-潢
+潢⊏
 㴌</t>
         </is>
       </c>
@@ -2934,7 +2934,8 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應</t>
+          <t xml:space="preserve">應
+ﾉ</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -2969,7 +2970,8 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌
+ﾉ</t>
         </is>
       </c>
       <c r="G14" s="24"/>

--- a/sheets/조재수대금교본/검수/봄날은 간다.xlsx
+++ b/sheets/조재수대금교본/검수/봄날은 간다.xlsx
@@ -2537,17 +2537,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
